--- a/MU/Test upload format/Normal/2029 - 2030/Q3 28-29.xlsx
+++ b/MU/Test upload format/Normal/2029 - 2030/Q3 28-29.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="496" uniqueCount="123">
   <si>
     <t>loancat</t>
   </si>
@@ -146,16 +146,13 @@
     <t>WhetherThirdPartyGuaranteeObtained</t>
   </si>
   <si>
-    <t>BusinessLoansOutstandAtSanAsPerCreditAmt</t>
-  </si>
-  <si>
     <t>HomeStay</t>
   </si>
   <si>
-    <t>TP</t>
-  </si>
-  <si>
-    <t>TP01</t>
+    <t>K</t>
+  </si>
+  <si>
+    <t>CR702</t>
   </si>
   <si>
     <t>F</t>
@@ -167,40 +164,238 @@
     <t>1</t>
   </si>
   <si>
+    <t>123 Main Street</t>
+  </si>
+  <si>
+    <t>SBIN0001234</t>
+  </si>
+  <si>
+    <t>Q3CRCGFEE02</t>
+  </si>
+  <si>
+    <t>800000</t>
+  </si>
+  <si>
+    <t>01-07-2026</t>
+  </si>
+  <si>
+    <t>50000</t>
+  </si>
+  <si>
+    <t>90000</t>
+  </si>
+  <si>
+    <t>AQPPL5</t>
+  </si>
+  <si>
+    <t>1234567802</t>
+  </si>
+  <si>
+    <t>1237</t>
+  </si>
+  <si>
+    <t>T</t>
+  </si>
+  <si>
+    <t>CR703</t>
+  </si>
+  <si>
+    <t>Q3CRCGFEE03</t>
+  </si>
+  <si>
+    <t>500000</t>
+  </si>
+  <si>
+    <t>60000</t>
+  </si>
+  <si>
+    <t>AQPPL2141K</t>
+  </si>
+  <si>
+    <t>1234567804</t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>CR704</t>
+  </si>
+  <si>
     <t>124 Main Street</t>
   </si>
   <si>
     <t>SBIN0001235</t>
   </si>
   <si>
-    <t>TP0101</t>
-  </si>
-  <si>
-    <t>900900.44</t>
-  </si>
-  <si>
-    <t>01-12-2028</t>
-  </si>
-  <si>
-    <t>9030.76</t>
-  </si>
-  <si>
-    <t>1000</t>
-  </si>
-  <si>
-    <t>AQPPL2141K</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>1237</t>
-  </si>
-  <si>
-    <t>TP02</t>
-  </si>
-  <si>
-    <t>TP0102</t>
+    <t>Q3CRCGFEE04</t>
+  </si>
+  <si>
+    <t>100000</t>
+  </si>
+  <si>
+    <t>70000</t>
+  </si>
+  <si>
+    <t>80000</t>
+  </si>
+  <si>
+    <t>AQPPL2144K</t>
+  </si>
+  <si>
+    <t>CR705</t>
+  </si>
+  <si>
+    <t>Q3CRCGFEE05</t>
+  </si>
+  <si>
+    <t>900000</t>
+  </si>
+  <si>
+    <t>CR706</t>
+  </si>
+  <si>
+    <t>Q3CRCGFEE06</t>
+  </si>
+  <si>
+    <t>CR707</t>
+  </si>
+  <si>
+    <t>Q3CRCGFEE07</t>
+  </si>
+  <si>
+    <t>CR709</t>
+  </si>
+  <si>
+    <t>Q3CRCGFEE08</t>
+  </si>
+  <si>
+    <t>120000</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>CR710</t>
+  </si>
+  <si>
+    <t>Q3CRCGFEE09</t>
+  </si>
+  <si>
+    <t>130000</t>
+  </si>
+  <si>
+    <t>CR711</t>
+  </si>
+  <si>
+    <t>Q3CRCGFEE10</t>
+  </si>
+  <si>
+    <t>140000</t>
+  </si>
+  <si>
+    <t>CR712</t>
+  </si>
+  <si>
+    <t>Q3CRCGFEE11</t>
+  </si>
+  <si>
+    <t>01-08-2026</t>
+  </si>
+  <si>
+    <t>15000</t>
+  </si>
+  <si>
+    <t>CR713</t>
+  </si>
+  <si>
+    <t>Q3CRCGFEE12</t>
+  </si>
+  <si>
+    <t>160000</t>
+  </si>
+  <si>
+    <t>CR715</t>
+  </si>
+  <si>
+    <t>Q3CRCGFEE13</t>
+  </si>
+  <si>
+    <t>180000</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>CR716</t>
+  </si>
+  <si>
+    <t>Q3CRCGFEE14</t>
+  </si>
+  <si>
+    <t>19000</t>
+  </si>
+  <si>
+    <t>CR717</t>
+  </si>
+  <si>
+    <t>Q3CRCGFEE15</t>
+  </si>
+  <si>
+    <t>200000</t>
+  </si>
+  <si>
+    <t>CR718</t>
+  </si>
+  <si>
+    <t>Q3CRCGFEE16</t>
+  </si>
+  <si>
+    <t>1000000</t>
+  </si>
+  <si>
+    <t>210000</t>
+  </si>
+  <si>
+    <t>CR720</t>
+  </si>
+  <si>
+    <t>Q3CRCGFEE17</t>
+  </si>
+  <si>
+    <t>10-08-2026</t>
+  </si>
+  <si>
+    <t>230000</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>CR721</t>
+  </si>
+  <si>
+    <t>Q3CRCGFEE18</t>
+  </si>
+  <si>
+    <t>240000</t>
+  </si>
+  <si>
+    <t>CR722</t>
+  </si>
+  <si>
+    <t>Q3CRCGFEE19</t>
+  </si>
+  <si>
+    <t>25000</t>
+  </si>
+  <si>
+    <t>CR723</t>
+  </si>
+  <si>
+    <t>Q3CRCGFEE20</t>
+  </si>
+  <si>
+    <t>26000</t>
   </si>
 </sst>
 </file>
@@ -213,7 +408,7 @@
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -228,12 +423,6 @@
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color indexed="8"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -380,12 +569,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -592,9 +787,7 @@
       <top style="thin">
         <color auto="1"/>
       </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -733,155 +926,158 @@
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1203,8 +1399,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AO3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="2"/>
+  <dimension ref="A1:AN20"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="14.4285714285714" customWidth="1"/>
     <col min="16" max="16" width="20" customWidth="1"/>
@@ -1215,107 +1411,107 @@
     <col min="35" max="35" width="20.1428571428571" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:41">
-      <c r="A1" s="3" t="s">
+    <row r="1" s="1" customFormat="1" spans="1:40">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="O1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="P1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="Q1" s="2" t="s">
         <v>16</v>
       </c>
       <c r="R1" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="S1" s="2" t="s">
         <v>18</v>
       </c>
       <c r="T1" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="3" t="s">
+      <c r="U1" s="2" t="s">
         <v>20</v>
       </c>
       <c r="V1" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="3" t="s">
+      <c r="W1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="3" t="s">
+      <c r="X1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="3" t="s">
+      <c r="Y1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="3" t="s">
+      <c r="Z1" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="3" t="s">
+      <c r="AA1" s="2" t="s">
         <v>26</v>
       </c>
       <c r="AB1" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="3" t="s">
+      <c r="AC1" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="3" t="s">
+      <c r="AD1" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="3" t="s">
+      <c r="AE1" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="3" t="s">
+      <c r="AF1" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="3" t="s">
+      <c r="AG1" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="3" t="s">
+      <c r="AH1" s="2" t="s">
         <v>33</v>
       </c>
       <c r="AI1" s="4" t="s">
@@ -1327,245 +1523,2066 @@
       <c r="AK1" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="AL1" s="2" t="s">
+      <c r="AL1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="2" t="s">
+      <c r="AM1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="AN1" s="2" t="s">
+      <c r="AN1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" s="2" t="s">
+    </row>
+    <row r="2" s="1" customFormat="1" spans="1:40">
+      <c r="A2" s="7" t="s">
         <v>40</v>
       </c>
+      <c r="B2" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2" s="7">
+        <v>1</v>
+      </c>
+      <c r="D2" s="7">
+        <v>1</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H2" s="7">
+        <v>1</v>
+      </c>
+      <c r="I2" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="J2" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="K2" s="7">
+        <v>209</v>
+      </c>
+      <c r="L2" s="7">
+        <v>233</v>
+      </c>
+      <c r="M2" s="7">
+        <v>10</v>
+      </c>
+      <c r="N2" s="7">
+        <v>800026</v>
+      </c>
+      <c r="O2" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="P2" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q2" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="R2" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="S2" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="T2" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="U2" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="V2" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="W2" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="X2" s="7"/>
+      <c r="Y2" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z2" s="7"/>
+      <c r="AA2" s="7"/>
+      <c r="AB2" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC2" s="7">
+        <v>0</v>
+      </c>
+      <c r="AD2" s="7">
+        <v>1</v>
+      </c>
+      <c r="AE2" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="AF2" s="7"/>
+      <c r="AG2" s="7"/>
+      <c r="AH2" s="7"/>
+      <c r="AI2" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="AJ2" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="AK2" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AL2" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AM2" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AN2" s="7" t="s">
+        <v>43</v>
+      </c>
     </row>
-    <row r="2" s="2" customFormat="1" spans="1:41">
-      <c r="A2" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B2" s="8" t="s">
+    <row r="3" s="1" customFormat="1" spans="1:40">
+      <c r="A3" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C3" s="7">
+        <v>1</v>
+      </c>
+      <c r="D3" s="7">
+        <v>1</v>
+      </c>
+      <c r="E3" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="C2" s="8">
-        <v>1</v>
-      </c>
-      <c r="D2" s="8">
-        <v>1</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8" t="s">
+      <c r="F3" s="7"/>
+      <c r="G3" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H3" s="7">
+        <v>1</v>
+      </c>
+      <c r="I3" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="H2" s="8">
-        <v>1</v>
-      </c>
-      <c r="I2" s="8" t="s">
+      <c r="J3" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="J2" s="8" t="s">
+      <c r="K3" s="7">
+        <v>209</v>
+      </c>
+      <c r="L3" s="7">
+        <v>233</v>
+      </c>
+      <c r="M3" s="7">
+        <v>10</v>
+      </c>
+      <c r="N3" s="7">
+        <v>800026</v>
+      </c>
+      <c r="O3" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="K2" s="8">
+      <c r="P3" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q3" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="R3" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="S3" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="T3" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="U3" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="V3" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="W3" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="X3" s="7"/>
+      <c r="Y3" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z3" s="7"/>
+      <c r="AA3" s="7"/>
+      <c r="AB3" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC3" s="7">
+        <v>0</v>
+      </c>
+      <c r="AD3" s="7">
+        <v>1</v>
+      </c>
+      <c r="AE3" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="AF3" s="7"/>
+      <c r="AG3" s="7"/>
+      <c r="AH3" s="7"/>
+      <c r="AI3" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="AJ3" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="AK3" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AL3" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AM3" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AN3" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" spans="1:40">
+      <c r="A4" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C4" s="7">
+        <v>1</v>
+      </c>
+      <c r="D4" s="7">
+        <v>1</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H4" s="7">
+        <v>1</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="K4" s="7">
         <v>209</v>
       </c>
-      <c r="L2" s="8">
+      <c r="L4" s="7">
         <v>233</v>
       </c>
-      <c r="M2" s="8">
+      <c r="M4" s="7">
         <v>10</v>
       </c>
-      <c r="N2" s="8">
+      <c r="N4" s="7">
         <v>800026</v>
       </c>
-      <c r="O2" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="P2" s="8" t="s">
+      <c r="O4" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="P4" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q4" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="R4" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="S4" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="T4" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="U4" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="V4" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="W4" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="X4" s="7"/>
+      <c r="Y4" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z4" s="7"/>
+      <c r="AA4" s="7"/>
+      <c r="AB4" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC4" s="7">
+        <v>0</v>
+      </c>
+      <c r="AD4" s="7">
+        <v>1</v>
+      </c>
+      <c r="AE4" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="AF4" s="7"/>
+      <c r="AG4" s="7"/>
+      <c r="AH4" s="7"/>
+      <c r="AI4" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="AJ4" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="AK4" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AL4" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AM4" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AN4" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" spans="1:40">
+      <c r="A5" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="C5" s="7">
+        <v>1</v>
+      </c>
+      <c r="D5" s="7">
+        <v>1</v>
+      </c>
+      <c r="E5" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="Q2" s="8" t="s">
+      <c r="F5" s="7"/>
+      <c r="G5" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H5" s="7">
+        <v>1</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="K5" s="7">
+        <v>209</v>
+      </c>
+      <c r="L5" s="7">
+        <v>233</v>
+      </c>
+      <c r="M5" s="7">
+        <v>10</v>
+      </c>
+      <c r="N5" s="7">
+        <v>800026</v>
+      </c>
+      <c r="O5" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="P5" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q5" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="R5" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="S5" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="T5" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="U5" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="V5" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="W5" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="X5" s="7"/>
+      <c r="Y5" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z5" s="7"/>
+      <c r="AA5" s="7"/>
+      <c r="AB5" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC5" s="7">
+        <v>0</v>
+      </c>
+      <c r="AD5" s="7">
+        <v>1</v>
+      </c>
+      <c r="AE5" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="AF5" s="7"/>
+      <c r="AG5" s="7"/>
+      <c r="AH5" s="7"/>
+      <c r="AI5" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="AJ5" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="AK5" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AL5" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AM5" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AN5" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" spans="1:40">
+      <c r="A6" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="C6" s="7">
+        <v>1</v>
+      </c>
+      <c r="D6" s="7">
+        <v>1</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H6" s="7">
+        <v>1</v>
+      </c>
+      <c r="I6" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="J6" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="K6" s="7">
+        <v>209</v>
+      </c>
+      <c r="L6" s="7">
+        <v>233</v>
+      </c>
+      <c r="M6" s="7">
+        <v>10</v>
+      </c>
+      <c r="N6" s="7">
+        <v>800026</v>
+      </c>
+      <c r="O6" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="P6" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q6" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="R6" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="R2" s="9" t="s">
+      <c r="S6" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="S2" s="2" t="s">
+      <c r="T6" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="U6" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="V6" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="T2" s="2" t="s">
+      <c r="W6" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="X6" s="7"/>
+      <c r="Y6" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z6" s="7"/>
+      <c r="AA6" s="7"/>
+      <c r="AB6" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC6" s="7">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="7">
+        <v>1</v>
+      </c>
+      <c r="AE6" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="AF6" s="7"/>
+      <c r="AG6" s="7"/>
+      <c r="AH6" s="7"/>
+      <c r="AI6" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="AJ6" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="AK6" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AL6" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AM6" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AN6" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" spans="1:40">
+      <c r="A7" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="C7" s="7">
+        <v>1</v>
+      </c>
+      <c r="D7" s="7">
+        <v>1</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H7" s="7">
+        <v>1</v>
+      </c>
+      <c r="I7" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="J7" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="K7" s="7">
+        <v>209</v>
+      </c>
+      <c r="L7" s="7">
+        <v>233</v>
+      </c>
+      <c r="M7" s="7">
+        <v>10</v>
+      </c>
+      <c r="N7" s="7">
+        <v>800026</v>
+      </c>
+      <c r="O7" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="P7" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q7" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="R7" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="S7" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="T7" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="U7" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="V7" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="W7" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="X7" s="7"/>
+      <c r="Y7" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z7" s="7"/>
+      <c r="AA7" s="7"/>
+      <c r="AB7" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC7" s="7">
+        <v>0</v>
+      </c>
+      <c r="AD7" s="7">
+        <v>1</v>
+      </c>
+      <c r="AE7" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="AF7" s="7"/>
+      <c r="AG7" s="7"/>
+      <c r="AH7" s="7"/>
+      <c r="AI7" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="AJ7" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="AK7" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AL7" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AM7" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AN7" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" spans="1:40">
+      <c r="A8" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="C8" s="7">
+        <v>1</v>
+      </c>
+      <c r="D8" s="7">
+        <v>1</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H8" s="7">
+        <v>1</v>
+      </c>
+      <c r="I8" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="J8" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="K8" s="7">
+        <v>209</v>
+      </c>
+      <c r="L8" s="7">
+        <v>233</v>
+      </c>
+      <c r="M8" s="7">
+        <v>10</v>
+      </c>
+      <c r="N8" s="7">
+        <v>800026</v>
+      </c>
+      <c r="O8" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="P8" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q8" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="R8" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="S8" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="T8" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="U8" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="V8" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="W8" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="X8" s="7"/>
+      <c r="Y8" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z8" s="7"/>
+      <c r="AA8" s="7"/>
+      <c r="AB8" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="AC8" s="7">
+        <v>0</v>
+      </c>
+      <c r="AD8" s="7">
+        <v>1</v>
+      </c>
+      <c r="AE8" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="AF8" s="7"/>
+      <c r="AG8" s="7"/>
+      <c r="AH8" s="7"/>
+      <c r="AI8" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="AJ8" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="AK8" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AL8" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AM8" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AN8" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" spans="1:40">
+      <c r="A9" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="C9" s="7">
+        <v>1</v>
+      </c>
+      <c r="D9" s="7">
+        <v>1</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H9" s="7">
+        <v>1</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="J9" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="K9" s="7">
+        <v>209</v>
+      </c>
+      <c r="L9" s="7">
+        <v>233</v>
+      </c>
+      <c r="M9" s="7">
+        <v>10</v>
+      </c>
+      <c r="N9" s="7">
+        <v>800026</v>
+      </c>
+      <c r="O9" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="P9" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q9" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="R9" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="S9" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="T9" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="U9" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="V9" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="W9" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="X9" s="7"/>
+      <c r="Y9" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z9" s="7"/>
+      <c r="AA9" s="7"/>
+      <c r="AB9" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="AC9" s="7">
+        <v>0</v>
+      </c>
+      <c r="AD9" s="7">
+        <v>1</v>
+      </c>
+      <c r="AE9" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="AF9" s="7"/>
+      <c r="AG9" s="7"/>
+      <c r="AH9" s="7"/>
+      <c r="AI9" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="AJ9" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="AK9" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AL9" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AM9" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AN9" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" spans="1:40">
+      <c r="A10" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="C10" s="7">
+        <v>1</v>
+      </c>
+      <c r="D10" s="7">
+        <v>1</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H10" s="7">
+        <v>1</v>
+      </c>
+      <c r="I10" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="J10" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="K10" s="7">
+        <v>209</v>
+      </c>
+      <c r="L10" s="7">
+        <v>233</v>
+      </c>
+      <c r="M10" s="7">
+        <v>10</v>
+      </c>
+      <c r="N10" s="7">
+        <v>800026</v>
+      </c>
+      <c r="O10" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="P10" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q10" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="R10" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="S10" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="T10" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="U10" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="V10" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="U2" s="2" t="s">
+      <c r="W10" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="X10" s="7"/>
+      <c r="Y10" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z10" s="7"/>
+      <c r="AA10" s="7"/>
+      <c r="AB10" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="AC10" s="7">
+        <v>0</v>
+      </c>
+      <c r="AD10" s="7">
+        <v>1</v>
+      </c>
+      <c r="AE10" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="AF10" s="7"/>
+      <c r="AG10" s="7"/>
+      <c r="AH10" s="7"/>
+      <c r="AI10" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="AJ10" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="AK10" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AL10" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AM10" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AN10" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" spans="1:40">
+      <c r="A11" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C11" s="7">
+        <v>1</v>
+      </c>
+      <c r="D11" s="7">
+        <v>1</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H11" s="7">
+        <v>1</v>
+      </c>
+      <c r="I11" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="J11" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="K11" s="7">
+        <v>209</v>
+      </c>
+      <c r="L11" s="7">
+        <v>233</v>
+      </c>
+      <c r="M11" s="7">
+        <v>10</v>
+      </c>
+      <c r="N11" s="7">
+        <v>800026</v>
+      </c>
+      <c r="O11" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="P11" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q11" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="R11" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="S11" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="T11" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="U11" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="V11" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="V2" s="2" t="s">
+      <c r="W11" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="X11" s="7"/>
+      <c r="Y11" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z11" s="7"/>
+      <c r="AA11" s="7"/>
+      <c r="AB11" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="AC11" s="7">
+        <v>0</v>
+      </c>
+      <c r="AD11" s="7">
+        <v>1</v>
+      </c>
+      <c r="AE11" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="AF11" s="7"/>
+      <c r="AG11" s="7"/>
+      <c r="AH11" s="7"/>
+      <c r="AI11" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="AJ11" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="AK11" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AL11" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AM11" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AN11" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" spans="1:40">
+      <c r="A12" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="C12" s="7">
+        <v>1</v>
+      </c>
+      <c r="D12" s="7">
+        <v>1</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H12" s="7">
+        <v>1</v>
+      </c>
+      <c r="I12" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="J12" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="K12" s="7">
+        <v>209</v>
+      </c>
+      <c r="L12" s="7">
+        <v>233</v>
+      </c>
+      <c r="M12" s="7">
+        <v>10</v>
+      </c>
+      <c r="N12" s="7">
+        <v>800026</v>
+      </c>
+      <c r="O12" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="P12" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q12" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="R12" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="S12" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="T12" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="U12" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="V12" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="W12" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="X12" s="7"/>
+      <c r="Y12" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z12" s="7"/>
+      <c r="AA12" s="7"/>
+      <c r="AB12" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="AC12" s="7">
+        <v>0</v>
+      </c>
+      <c r="AD12" s="7">
+        <v>1</v>
+      </c>
+      <c r="AE12" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="AF12" s="7"/>
+      <c r="AG12" s="7"/>
+      <c r="AH12" s="7"/>
+      <c r="AI12" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="AJ12" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="AK12" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AL12" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AM12" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AN12" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" spans="1:40">
+      <c r="A13" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="C13" s="7">
+        <v>1</v>
+      </c>
+      <c r="D13" s="7">
+        <v>1</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H13" s="7">
+        <v>1</v>
+      </c>
+      <c r="I13" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="J13" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="K13" s="7">
+        <v>209</v>
+      </c>
+      <c r="L13" s="7">
+        <v>233</v>
+      </c>
+      <c r="M13" s="7">
+        <v>10</v>
+      </c>
+      <c r="N13" s="7">
+        <v>800026</v>
+      </c>
+      <c r="O13" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="P13" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q13" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="R13" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="S13" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="T13" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="U13" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="V13" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="W13" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="X13" s="7"/>
+      <c r="Y13" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z13" s="7"/>
+      <c r="AA13" s="7"/>
+      <c r="AB13" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="AC13" s="7">
+        <v>0</v>
+      </c>
+      <c r="AD13" s="7">
+        <v>1</v>
+      </c>
+      <c r="AE13" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="AF13" s="7"/>
+      <c r="AG13" s="7"/>
+      <c r="AH13" s="7"/>
+      <c r="AI13" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="AJ13" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="AK13" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AL13" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AM13" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AN13" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" spans="1:40">
+      <c r="A14" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="C14" s="7">
+        <v>1</v>
+      </c>
+      <c r="D14" s="7">
+        <v>1</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="F14" s="7"/>
+      <c r="G14" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H14" s="7">
+        <v>1</v>
+      </c>
+      <c r="I14" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="J14" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="K14" s="7">
+        <v>209</v>
+      </c>
+      <c r="L14" s="7">
+        <v>233</v>
+      </c>
+      <c r="M14" s="7">
+        <v>10</v>
+      </c>
+      <c r="N14" s="7">
+        <v>800026</v>
+      </c>
+      <c r="O14" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="P14" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q14" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="R14" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="S14" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="T14" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="U14" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="V14" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="W14" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="X14" s="7"/>
+      <c r="Y14" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z14" s="7"/>
+      <c r="AA14" s="7"/>
+      <c r="AB14" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="AC14" s="7">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="7">
+        <v>1</v>
+      </c>
+      <c r="AE14" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="AF14" s="7"/>
+      <c r="AG14" s="7"/>
+      <c r="AH14" s="7"/>
+      <c r="AI14" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="AJ14" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="AK14" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AL14" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AM14" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AN14" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" spans="1:40">
+      <c r="A15" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="C15" s="7">
+        <v>1</v>
+      </c>
+      <c r="D15" s="7">
+        <v>1</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H15" s="7">
+        <v>1</v>
+      </c>
+      <c r="I15" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="J15" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="K15" s="7">
+        <v>209</v>
+      </c>
+      <c r="L15" s="7">
+        <v>233</v>
+      </c>
+      <c r="M15" s="7">
+        <v>10</v>
+      </c>
+      <c r="N15" s="7">
+        <v>800026</v>
+      </c>
+      <c r="O15" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="P15" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q15" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="R15" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="S15" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="T15" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="U15" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="V15" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="W15" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="X15" s="7"/>
+      <c r="Y15" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z15" s="7"/>
+      <c r="AA15" s="7"/>
+      <c r="AB15" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="AC15" s="7">
+        <v>0</v>
+      </c>
+      <c r="AD15" s="7">
+        <v>1</v>
+      </c>
+      <c r="AE15" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="W2" s="2" t="s">
+      <c r="AF15" s="7"/>
+      <c r="AG15" s="7"/>
+      <c r="AH15" s="7"/>
+      <c r="AI15" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="AJ15" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="AK15" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AL15" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AM15" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AN15" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" spans="1:40">
+      <c r="A16" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="C16" s="7">
+        <v>1</v>
+      </c>
+      <c r="D16" s="7">
+        <v>1</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="F16" s="7"/>
+      <c r="G16" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H16" s="7">
+        <v>1</v>
+      </c>
+      <c r="I16" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="X2" s="8"/>
-      <c r="Y2" s="8" t="s">
+      <c r="J16" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="K16" s="7">
+        <v>209</v>
+      </c>
+      <c r="L16" s="7">
+        <v>233</v>
+      </c>
+      <c r="M16" s="7">
+        <v>10</v>
+      </c>
+      <c r="N16" s="7">
+        <v>800026</v>
+      </c>
+      <c r="O16" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="P16" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q16" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="R16" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="S16" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="T16" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="U16" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="V16" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="W16" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="X16" s="7"/>
+      <c r="Y16" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z16" s="7"/>
+      <c r="AA16" s="7"/>
+      <c r="AB16" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="AC16" s="7">
+        <v>0</v>
+      </c>
+      <c r="AD16" s="7">
+        <v>1</v>
+      </c>
+      <c r="AE16" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="AF16" s="7"/>
+      <c r="AG16" s="7"/>
+      <c r="AH16" s="7"/>
+      <c r="AI16" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="AJ16" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="AK16" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AL16" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AM16" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AN16" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" spans="1:40">
+      <c r="A17" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="C17" s="7">
+        <v>1</v>
+      </c>
+      <c r="D17" s="7">
+        <v>1</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="F17" s="7"/>
+      <c r="G17" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H17" s="7">
+        <v>1</v>
+      </c>
+      <c r="I17" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="Z2" s="8"/>
-      <c r="AA2" s="8"/>
-      <c r="AB2" s="8">
-        <v>1</v>
-      </c>
-      <c r="AC2" s="8">
+      <c r="J17" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="K17" s="7">
+        <v>209</v>
+      </c>
+      <c r="L17" s="7">
+        <v>233</v>
+      </c>
+      <c r="M17" s="7">
+        <v>10</v>
+      </c>
+      <c r="N17" s="7">
+        <v>800026</v>
+      </c>
+      <c r="O17" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="P17" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="Q17" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="R17" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="S17" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="T17" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="U17" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="V17" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="W17" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="X17" s="7"/>
+      <c r="Y17" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z17" s="7"/>
+      <c r="AA17" s="7"/>
+      <c r="AB17" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AC17" s="7">
         <v>0</v>
       </c>
-      <c r="AD2" s="8">
-        <v>1</v>
-      </c>
-      <c r="AE2" s="8" t="s">
+      <c r="AD17" s="7">
+        <v>1</v>
+      </c>
+      <c r="AE17" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="AF17" s="7"/>
+      <c r="AG17" s="7"/>
+      <c r="AH17" s="7"/>
+      <c r="AI17" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="AF2" s="7" t="s">
+      <c r="AJ17" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="AG2" s="10" t="s">
+      <c r="AK17" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AL17" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AM17" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AN17" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" spans="1:40">
+      <c r="A18" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="C18" s="7">
+        <v>1</v>
+      </c>
+      <c r="D18" s="7">
+        <v>1</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="F18" s="7"/>
+      <c r="G18" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H18" s="7">
+        <v>1</v>
+      </c>
+      <c r="I18" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="J18" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="K18" s="7">
+        <v>209</v>
+      </c>
+      <c r="L18" s="7">
+        <v>233</v>
+      </c>
+      <c r="M18" s="7">
+        <v>10</v>
+      </c>
+      <c r="N18" s="7">
+        <v>800026</v>
+      </c>
+      <c r="O18" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="P18" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q18" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="R18" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="S18" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="T18" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="U18" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="V18" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="W18" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="X18" s="7"/>
+      <c r="Y18" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z18" s="7"/>
+      <c r="AA18" s="7"/>
+      <c r="AB18" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AC18" s="7">
+        <v>0</v>
+      </c>
+      <c r="AD18" s="7">
+        <v>1</v>
+      </c>
+      <c r="AE18" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="AF18" s="7"/>
+      <c r="AG18" s="7"/>
+      <c r="AH18" s="7"/>
+      <c r="AI18" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="AJ18" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="AH2" s="10" t="s">
+      <c r="AK18" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AL18" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AM18" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AN18" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="19" s="1" customFormat="1" spans="1:40">
+      <c r="A19" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="C19" s="7">
+        <v>1</v>
+      </c>
+      <c r="D19" s="7">
+        <v>1</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="F19" s="7"/>
+      <c r="G19" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H19" s="7">
+        <v>1</v>
+      </c>
+      <c r="I19" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="AI2" s="11">
-        <v>1234567893</v>
-      </c>
-      <c r="AJ2" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="AK2" s="8" t="s">
+      <c r="J19" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="K19" s="7">
+        <v>209</v>
+      </c>
+      <c r="L19" s="7">
+        <v>233</v>
+      </c>
+      <c r="M19" s="7">
+        <v>10</v>
+      </c>
+      <c r="N19" s="7">
+        <v>800026</v>
+      </c>
+      <c r="O19" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="P19" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q19" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="R19" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="S19" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="T19" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="U19" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="V19" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="W19" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="X19" s="7"/>
+      <c r="Y19" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z19" s="7"/>
+      <c r="AA19" s="7"/>
+      <c r="AB19" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AC19" s="7">
+        <v>0</v>
+      </c>
+      <c r="AD19" s="7">
+        <v>1</v>
+      </c>
+      <c r="AE19" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="AF19" s="7"/>
+      <c r="AG19" s="7"/>
+      <c r="AH19" s="7"/>
+      <c r="AI19" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="AJ19" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="AK19" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AL19" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AM19" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AN19" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="20" s="1" customFormat="1" spans="1:40">
+      <c r="A20" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="C20" s="7">
+        <v>1</v>
+      </c>
+      <c r="D20" s="7">
+        <v>1</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="F20" s="7"/>
+      <c r="G20" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H20" s="7">
+        <v>1</v>
+      </c>
+      <c r="I20" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="AL2" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="AM2" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="AO2" s="8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="3" s="2" customFormat="1" spans="1:41">
-      <c r="A3" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="C3" s="8">
-        <v>1</v>
-      </c>
-      <c r="D3" s="8">
-        <v>1</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="H3" s="8">
-        <v>1</v>
-      </c>
-      <c r="I3" s="8" t="s">
+      <c r="J20" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="J3" s="8" t="s">
+      <c r="K20" s="7">
+        <v>209</v>
+      </c>
+      <c r="L20" s="7">
+        <v>233</v>
+      </c>
+      <c r="M20" s="7">
+        <v>10</v>
+      </c>
+      <c r="N20" s="7">
+        <v>800026</v>
+      </c>
+      <c r="O20" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="K3" s="8">
-        <v>209</v>
-      </c>
-      <c r="L3" s="8">
-        <v>233</v>
-      </c>
-      <c r="M3" s="8">
-        <v>10</v>
-      </c>
-      <c r="N3" s="8">
-        <v>800026</v>
-      </c>
-      <c r="O3" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="P3" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q3" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="R3" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="S3" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="T3" s="2" t="s">
+      <c r="P20" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q20" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="R20" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="S20" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="T20" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="U20" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="V20" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="U3" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="V3" s="2" t="s">
+      <c r="W20" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="X20" s="7"/>
+      <c r="Y20" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z20" s="7"/>
+      <c r="AA20" s="7"/>
+      <c r="AB20" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AC20" s="7">
+        <v>0</v>
+      </c>
+      <c r="AD20" s="7">
+        <v>1</v>
+      </c>
+      <c r="AE20" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="W3" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="X3" s="8"/>
-      <c r="Y3" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z3" s="8"/>
-      <c r="AA3" s="8"/>
-      <c r="AB3" s="8">
-        <v>1</v>
-      </c>
-      <c r="AC3" s="8">
-        <v>0</v>
-      </c>
-      <c r="AD3" s="8">
-        <v>1</v>
-      </c>
-      <c r="AE3" s="8" t="s">
+      <c r="AF20" s="7"/>
+      <c r="AG20" s="7"/>
+      <c r="AH20" s="7"/>
+      <c r="AI20" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="AF3" s="7" t="s">
+      <c r="AJ20" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="AG3" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="AH3" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="AI3" s="11">
-        <v>1234567893</v>
-      </c>
-      <c r="AJ3" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="AK3" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="AL3" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="AM3" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="AO3" s="8" t="s">
-        <v>44</v>
+      <c r="AK20" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AL20" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AM20" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AN20" s="7" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>
